--- a/depence_bedel.xlsx
+++ b/depence_bedel.xlsx
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1351" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="60">
   <si>
     <t>depence</t>
   </si>
@@ -241,6 +241,12 @@
   <si>
     <t>BD0123TU</t>
   </si>
+  <si>
+    <t>BD0124DU</t>
+  </si>
+  <si>
+    <t>BD01247F</t>
+  </si>
 </sst>
 </file>
 
@@ -290,7 +296,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -311,10 +317,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -14161,7 +14170,7 @@
 
 <file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="15.5703125" defaultRowHeight="18.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16.140625" style="7" bestFit="1" customWidth="1"/>
@@ -14184,8 +14193,8 @@
         <v>7</v>
       </c>
       <c r="B2" s="7">
-        <f>SUM(C8:C1919)</f>
-        <v>535</v>
+        <f>SUM(C8:C1918)</f>
+        <v>1615</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18.75" customHeight="1">
@@ -14194,7 +14203,7 @@
       </c>
       <c r="B3" s="7">
         <f>SUM(B1-B2)</f>
-        <v>1220</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18.75" customHeight="1">
@@ -14209,7 +14218,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" ht="18.75" customHeight="1">
-      <c r="A8" s="11">
+      <c r="A8" s="10">
         <v>46045</v>
       </c>
       <c r="B8" s="7" t="s">
@@ -14220,7 +14229,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" ht="18.75" customHeight="1">
-      <c r="A9" s="11">
+      <c r="A9" s="10">
         <v>46045</v>
       </c>
       <c r="B9" s="7" t="s">
@@ -14231,7 +14240,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" ht="18.75" customHeight="1">
-      <c r="A10" s="11">
+      <c r="A10" s="10">
         <v>46045</v>
       </c>
       <c r="B10" s="7" t="s">
@@ -14242,7 +14251,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" ht="18.75" customHeight="1">
-      <c r="A11" s="11">
+      <c r="A11" s="10">
         <v>46045</v>
       </c>
       <c r="B11" s="7" t="s">
@@ -14253,7 +14262,7 @@
       </c>
     </row>
     <row r="13" spans="1:4" ht="18.75" customHeight="1">
-      <c r="A13" s="11">
+      <c r="A13" s="10">
         <v>46046</v>
       </c>
       <c r="B13" s="7" t="s">
@@ -14267,16 +14276,65 @@
       </c>
     </row>
     <row r="14" spans="1:4" ht="18.75" customHeight="1">
-      <c r="A14" s="11"/>
-    </row>
-    <row r="15" spans="1:4" ht="18.75" customHeight="1">
-      <c r="A15" s="11"/>
+      <c r="A14" s="10">
+        <v>46046</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="7">
+        <v>370</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" s="9" customFormat="1" ht="18.75" customHeight="1">
+      <c r="A15" s="10">
+        <v>46046</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="9">
+        <v>370</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="16" spans="1:4" ht="18.75" customHeight="1">
-      <c r="A16" s="11"/>
-    </row>
-    <row r="17" spans="1:1" ht="18.75" customHeight="1">
-      <c r="A17" s="11"/>
+      <c r="A16" s="10">
+        <v>46046</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="9">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A17" s="10">
+        <v>46046</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A18" s="10">
+        <v>46046</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="7">
+        <v>60</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15693,30 +15751,30 @@
       <c r="A1" s="3"/>
     </row>
     <row r="2" spans="1:9" s="4" customFormat="1" ht="18.75" customHeight="1">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="9">
+      <c r="B2" s="12"/>
+      <c r="C2" s="11">
         <f>SUM(C6:C30)</f>
         <v>300</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="10"/>
-      <c r="I2" s="9">
+      <c r="H2" s="12"/>
+      <c r="I2" s="11">
         <f>SUM(I6:I20)</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="4" customFormat="1" ht="18.75" customHeight="1">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="9"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="9"/>
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="11"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="11"/>
     </row>
     <row r="5" spans="1:9" ht="18.75" customHeight="1">
       <c r="A5" s="1" t="s">

--- a/depence_bedel.xlsx
+++ b/depence_bedel.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="20730" windowHeight="11760" firstSheet="40" activeTab="47"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="20730" windowHeight="11760" firstSheet="53" activeTab="60"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -55,6 +55,19 @@
     <sheet name="Feuil1 (44)" sheetId="46" r:id="rId46"/>
     <sheet name="Feuil1 (45)" sheetId="47" r:id="rId47"/>
     <sheet name="Feuil1 (46)" sheetId="48" r:id="rId48"/>
+    <sheet name="Feuil1 (47)" sheetId="49" r:id="rId49"/>
+    <sheet name="Feuil1 (48)" sheetId="50" r:id="rId50"/>
+    <sheet name="Feuil1 (49)" sheetId="51" r:id="rId51"/>
+    <sheet name="Feuil1 (50)" sheetId="52" r:id="rId52"/>
+    <sheet name="Feuil1 (51)" sheetId="53" r:id="rId53"/>
+    <sheet name="Feuil1 (52)" sheetId="54" r:id="rId54"/>
+    <sheet name="Feuil1 (53)" sheetId="55" r:id="rId55"/>
+    <sheet name="Feuil1 (54)" sheetId="56" r:id="rId56"/>
+    <sheet name="Feuil1 (55)" sheetId="57" r:id="rId57"/>
+    <sheet name="Feuil1 (56)" sheetId="58" r:id="rId58"/>
+    <sheet name="Feuil1 (57)" sheetId="59" r:id="rId59"/>
+    <sheet name="Feuil1 (58)" sheetId="60" r:id="rId60"/>
+    <sheet name="Feuil1 (59)" sheetId="61" r:id="rId61"/>
   </sheets>
   <calcPr calcId="124519"/>
   <extLst>
@@ -66,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1657" uniqueCount="74">
   <si>
     <t>depence</t>
   </si>
@@ -247,6 +260,48 @@
   <si>
     <t>BD01247F</t>
   </si>
+  <si>
+    <t>BD0126KY</t>
+  </si>
+  <si>
+    <t>chei5</t>
+  </si>
+  <si>
+    <t>dickdir</t>
+  </si>
+  <si>
+    <t>prise</t>
+  </si>
+  <si>
+    <t>melange</t>
+  </si>
+  <si>
+    <t>Melange</t>
+  </si>
+  <si>
+    <t>lv6our</t>
+  </si>
+  <si>
+    <t>Client</t>
+  </si>
+  <si>
+    <t>BD0304NJ</t>
+  </si>
+  <si>
+    <t>CHAM5</t>
+  </si>
+  <si>
+    <t>cleint</t>
+  </si>
+  <si>
+    <t>BD0327BZ</t>
+  </si>
+  <si>
+    <t>BD0327MR</t>
+  </si>
+  <si>
+    <t>Chei5</t>
+  </si>
 </sst>
 </file>
 
@@ -296,7 +351,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -318,6 +373,213 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -14170,7 +14432,7 @@
 
 <file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="15.5703125" defaultRowHeight="18.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16.140625" style="7" bestFit="1" customWidth="1"/>
@@ -14194,7 +14456,7 @@
       </c>
       <c r="B2" s="7">
         <f>SUM(C8:C1918)</f>
-        <v>1615</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18.75" customHeight="1">
@@ -14203,7 +14465,7 @@
       </c>
       <c r="B3" s="7">
         <f>SUM(B1-B2)</f>
-        <v>140</v>
+        <v>-160</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18.75" customHeight="1">
@@ -14314,27 +14576,330 @@
         <v>180</v>
       </c>
     </row>
+    <row r="17" spans="1:4" ht="18.75" customHeight="1">
+      <c r="A17" s="10">
+        <v>46046</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="18.75" customHeight="1">
+      <c r="A18" s="10">
+        <v>46046</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="18.75" customHeight="1">
+      <c r="A20" s="10">
+        <v>46047</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="11">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="18.75" customHeight="1">
+      <c r="A21" s="10">
+        <v>46047</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="11">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="18.75" customHeight="1">
+      <c r="A22" s="10">
+        <v>46047</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="18.75" customHeight="1">
+      <c r="A23" s="10">
+        <v>46047</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="18.75" customHeight="1">
+      <c r="A25" s="10"/>
+      <c r="B25" s="11"/>
+      <c r="D25" s="11"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D31"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="15.5703125" defaultRowHeight="18.75" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="16.140625" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" style="12" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="15.5703125" style="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="18.75" customHeight="1">
+      <c r="A1" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="12">
+        <f>2000-160</f>
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="18.75" customHeight="1">
+      <c r="A2" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="12">
+        <f>SUM(C7:C1900)</f>
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="18.75" customHeight="1">
+      <c r="A3" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="12">
+        <f>SUM(B1-B2)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="18.75" customHeight="1">
+      <c r="A6" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="18.75" customHeight="1">
+      <c r="A7" s="10">
+        <v>46048</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="12">
+        <v>360</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="18.75" customHeight="1">
+      <c r="A8" s="10">
+        <v>46048</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="12">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="18.75" customHeight="1">
+      <c r="A9" s="10">
+        <v>46048</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="18.75" customHeight="1">
+      <c r="A10" s="10">
+        <v>46048</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="18.75" customHeight="1">
+      <c r="A11" s="10">
+        <v>46048</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="18.75" customHeight="1">
+      <c r="A12" s="10">
+        <v>46048</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="12">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="18.75" customHeight="1">
+      <c r="A14" s="10">
+        <v>46049</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="12">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="18.75" customHeight="1">
+      <c r="A15" s="10">
+        <v>46049</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="18.75" customHeight="1">
+      <c r="A16" s="10">
+        <v>46049</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="12">
+        <v>100</v>
+      </c>
+    </row>
     <row r="17" spans="1:3" ht="18.75" customHeight="1">
       <c r="A17" s="10">
-        <v>46046</v>
-      </c>
-      <c r="B17" s="9" t="s">
+        <v>46049</v>
+      </c>
+      <c r="B17" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C17" s="12">
         <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="18.75" customHeight="1">
       <c r="A18" s="10">
-        <v>46046</v>
-      </c>
-      <c r="B18" s="9" t="s">
+        <v>46049</v>
+      </c>
+      <c r="B18" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="12">
         <v>60</v>
       </c>
+    </row>
+    <row r="20" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A20" s="10">
+        <v>46050</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="12">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A21" s="10">
+        <v>46050</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A22" s="10">
+        <v>46050</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A23" s="10">
+        <v>46050</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A24" s="10">
+        <v>46050</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" s="12">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A27" s="10"/>
+      <c r="B27" s="16"/>
+    </row>
+    <row r="28" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A28" s="10"/>
+      <c r="B28" s="16"/>
+    </row>
+    <row r="29" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A29" s="10"/>
+      <c r="B29" s="16"/>
+    </row>
+    <row r="30" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A30" s="10"/>
+      <c r="B30" s="16"/>
+    </row>
+    <row r="31" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A31" s="10"/>
+      <c r="B31" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14688,6 +15253,2575 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C31"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="15.5703125" defaultRowHeight="18.75" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="16.140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" style="16" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="15.5703125" style="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A1" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="16">
+        <f>2000+10</f>
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A2" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="16">
+        <f>SUM(C7:C1900)</f>
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A3" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="16">
+        <f>SUM(B1-B2)</f>
+        <v>190</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A6" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A7" s="10"/>
+    </row>
+    <row r="8" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A8" s="10">
+        <v>46051</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="16">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A9" s="10">
+        <v>46051</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="16">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A10" s="10">
+        <v>46051</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A11" s="10">
+        <v>46051</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A12" s="10">
+        <v>46051</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="16">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A14" s="10">
+        <v>46052</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="16">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A15" s="10">
+        <v>46052</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="16">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A16" s="10">
+        <v>46052</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A17" s="10">
+        <v>46052</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A19" s="10">
+        <v>46053</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="16">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A20" s="10">
+        <v>46053</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A21" s="10">
+        <v>46053</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="16">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A23" s="10">
+        <v>46054</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="16">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A24" s="10">
+        <v>46054</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="16">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A25" s="10">
+        <v>46054</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" s="16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A26" s="10">
+        <v>46054</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" s="16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A27" s="10">
+        <v>46054</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="16">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A28" s="10">
+        <v>46054</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28" s="16">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A29" s="10"/>
+    </row>
+    <row r="30" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A30" s="10"/>
+    </row>
+    <row r="31" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A31" s="10"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="15.5703125" defaultRowHeight="18.75" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="16.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" style="20" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="15.5703125" style="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A1" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="20">
+        <f>2000+190</f>
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A2" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="20">
+        <f>SUM(C7:C1885)</f>
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A3" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="20">
+        <f>SUM(B1-B2)</f>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A6" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A7" s="10"/>
+    </row>
+    <row r="8" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A8" s="10">
+        <v>46055</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="20">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A9" s="10">
+        <v>46055</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="20">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A10" s="10">
+        <v>46055</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="20">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A11" s="10">
+        <v>46055</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A12" s="10">
+        <v>46055</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A13" s="10">
+        <v>46055</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="20">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A14" s="10"/>
+    </row>
+    <row r="15" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A15" s="10">
+        <v>46056</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="22">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A16" s="10">
+        <v>46056</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="22">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A17" s="10">
+        <v>46056</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="22">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A18" s="10">
+        <v>46056</v>
+      </c>
+      <c r="B18" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="22">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A19" s="10">
+        <v>46056</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="22">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A21" s="10">
+        <v>46057</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="23">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A22" s="10">
+        <v>46057</v>
+      </c>
+      <c r="B22" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="23">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A23" s="10">
+        <v>46057</v>
+      </c>
+      <c r="B23" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="23">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A24" s="10">
+        <v>46057</v>
+      </c>
+      <c r="B24" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="23">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A25" s="10">
+        <v>46057</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="23">
+        <v>60</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="15.5703125" defaultRowHeight="18.75" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="16.140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" style="24" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" style="24" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="15.5703125" style="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A1" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="24">
+        <f>2000+320</f>
+        <v>2320</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A2" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="24">
+        <f>SUM(C8:C1873)</f>
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A3" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="24">
+        <f>SUM(B1-B2)</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A6" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A8" s="10">
+        <v>46058</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="24">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A9" s="10">
+        <v>46058</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="24">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A10" s="10">
+        <v>46058</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="24">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A11" s="10">
+        <v>46058</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="24">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A12" s="10">
+        <v>46058</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="24">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A13" s="10">
+        <v>46058</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="24">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A15" s="10">
+        <v>46059</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" s="24">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" s="26" customFormat="1" ht="18.75" customHeight="1">
+      <c r="A16" s="10">
+        <v>46059</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="26">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A17" s="10">
+        <v>46059</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="24">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A18" s="10">
+        <v>46059</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="24">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A19" s="10">
+        <v>46059</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="24">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A20" s="10">
+        <v>46059</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="24">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A22" s="10">
+        <v>46060</v>
+      </c>
+      <c r="B22" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="24">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A23" s="10">
+        <v>46060</v>
+      </c>
+      <c r="B23" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="24">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A24" s="10">
+        <v>46060</v>
+      </c>
+      <c r="B24" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="24">
+        <v>60</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C27"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="15.5703125" defaultRowHeight="18.75" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="16.140625" style="28" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" style="28" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" style="28" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="15.5703125" style="28"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A1" s="29" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="28">
+        <f>2000+80</f>
+        <v>2080</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A2" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="28">
+        <f>SUM(C7:C1875)</f>
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A3" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="28">
+        <f>SUM(B1-B2)</f>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A6" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A8" s="10">
+        <v>46061</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="28">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A9" s="10">
+        <v>46061</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="28">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A10" s="10">
+        <v>46061</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="28">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A11" s="10">
+        <v>46061</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="28">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A13" s="10">
+        <v>46062</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="30">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A14" s="10">
+        <v>46062</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="30">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A15" s="10">
+        <v>46062</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="30">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A16" s="10">
+        <v>46062</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="30">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" s="31" customFormat="1" ht="18.75" customHeight="1">
+      <c r="A18" s="10">
+        <v>46063</v>
+      </c>
+      <c r="B18" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" s="31">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A19" s="10">
+        <v>46063</v>
+      </c>
+      <c r="B19" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="28">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A20" s="10">
+        <v>46063</v>
+      </c>
+      <c r="B20" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="28">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A21" s="10">
+        <v>46063</v>
+      </c>
+      <c r="B21" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="28">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A22" s="10">
+        <v>46063</v>
+      </c>
+      <c r="B22" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="28">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A24" s="10">
+        <v>46064</v>
+      </c>
+      <c r="B24" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="28">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A25" s="10">
+        <v>46064</v>
+      </c>
+      <c r="B25" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="28">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A26" s="10">
+        <v>46064</v>
+      </c>
+      <c r="B26" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="28">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A27" s="10">
+        <v>46064</v>
+      </c>
+      <c r="B27" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" s="28">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C31"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="15.5703125" defaultRowHeight="18.75" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="16.140625" style="33" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" style="33" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" style="33" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="15.5703125" style="33"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A1" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="33">
+        <f>2000+240</f>
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A2" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="33">
+        <f>SUM(C7:C1858)</f>
+        <v>2360</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A3" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="33">
+        <f>SUM(B1-B2)</f>
+        <v>-120</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A6" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A8" s="10">
+        <v>46065</v>
+      </c>
+      <c r="B8" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="33">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A9" s="10">
+        <v>46065</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="33">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A10" s="10">
+        <v>46065</v>
+      </c>
+      <c r="B10" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="33">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A11" s="10">
+        <v>46065</v>
+      </c>
+      <c r="B11" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="33">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A13" s="10">
+        <v>46066</v>
+      </c>
+      <c r="B13" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="35">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A14" s="10">
+        <v>46066</v>
+      </c>
+      <c r="B14" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A15" s="10">
+        <v>46066</v>
+      </c>
+      <c r="B15" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A16" s="10">
+        <v>46066</v>
+      </c>
+      <c r="B16" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="35">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A18" s="10">
+        <v>46067</v>
+      </c>
+      <c r="B18" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="33">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" s="37" customFormat="1" ht="18.75" customHeight="1">
+      <c r="A19" s="10">
+        <v>46067</v>
+      </c>
+      <c r="B19" s="37" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="37">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A20" s="10">
+        <v>46067</v>
+      </c>
+      <c r="B20" s="36" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="33">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A22" s="10">
+        <v>46068</v>
+      </c>
+      <c r="B22" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="33">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A23" s="10">
+        <v>46068</v>
+      </c>
+      <c r="B23" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="33">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A24" s="10">
+        <v>46068</v>
+      </c>
+      <c r="B24" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="33">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A25" s="10">
+        <v>46068</v>
+      </c>
+      <c r="B25" s="38" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="33">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A27" s="10">
+        <v>46069</v>
+      </c>
+      <c r="B27" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="33">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A28" s="10">
+        <v>46069</v>
+      </c>
+      <c r="B28" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" s="33">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A29" s="10">
+        <v>46069</v>
+      </c>
+      <c r="B29" s="39" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" s="33">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A30" s="10">
+        <v>46069</v>
+      </c>
+      <c r="B30" s="39" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" s="33">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A31" s="10">
+        <v>46069</v>
+      </c>
+      <c r="B31" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31" s="33">
+        <v>60</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="15.5703125" defaultRowHeight="18.75" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="16.140625" style="40" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" style="40" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" style="40" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="15.5703125" style="40"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A1" s="41" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="40">
+        <f>2000-120</f>
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A2" s="41" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="40">
+        <f>SUM(C7:C1839)</f>
+        <v>2440</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A3" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="40">
+        <f>SUM(B1-B2)</f>
+        <v>-560</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A6" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="40" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="40" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A8" s="10">
+        <v>46070</v>
+      </c>
+      <c r="B8" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="40">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A9" s="10">
+        <v>46070</v>
+      </c>
+      <c r="B9" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="40">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A10" s="10">
+        <v>46070</v>
+      </c>
+      <c r="B10" s="40" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="40">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A11" s="10">
+        <v>46070</v>
+      </c>
+      <c r="B11" s="40" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="40">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A13" s="10">
+        <v>46071</v>
+      </c>
+      <c r="B13" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="42">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A14" s="10">
+        <v>46071</v>
+      </c>
+      <c r="B14" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="42">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A15" s="10">
+        <v>46071</v>
+      </c>
+      <c r="B15" s="42" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="42">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A16" s="10">
+        <v>46071</v>
+      </c>
+      <c r="B16" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="42">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A17" s="10">
+        <v>46071</v>
+      </c>
+      <c r="B17" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="40">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A19" s="10">
+        <v>46072</v>
+      </c>
+      <c r="B19" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="43">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A20" s="10">
+        <v>46072</v>
+      </c>
+      <c r="B20" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="43">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A21" s="10">
+        <v>46072</v>
+      </c>
+      <c r="B21" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="43">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A22" s="10">
+        <v>46072</v>
+      </c>
+      <c r="B22" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="43">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A23" s="10">
+        <v>46072</v>
+      </c>
+      <c r="B23" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="43">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A25" s="10">
+        <v>46073</v>
+      </c>
+      <c r="B25" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" s="40">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A26" s="10">
+        <v>46073</v>
+      </c>
+      <c r="B26" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="40">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A27" s="10">
+        <v>46073</v>
+      </c>
+      <c r="B27" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="40">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A28" s="10">
+        <v>46073</v>
+      </c>
+      <c r="B28" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" s="40">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A29" s="10">
+        <v>46073</v>
+      </c>
+      <c r="B29" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="C29" s="40">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A31" s="10">
+        <v>46074</v>
+      </c>
+      <c r="B31" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31" s="40">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A33" s="10">
+        <v>46075</v>
+      </c>
+      <c r="B33" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33" s="45">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A34" s="10">
+        <v>46075</v>
+      </c>
+      <c r="B34" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34" s="45">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A35" s="10">
+        <v>46075</v>
+      </c>
+      <c r="B35" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="C35" s="45">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="15.5703125" defaultRowHeight="18.75" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="16.140625" style="46" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" style="46" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" style="46" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="15.5703125" style="46"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A1" s="47" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="46">
+        <f>2000-560</f>
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A2" s="47" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="46">
+        <f>SUM(C7:C1814)</f>
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A3" s="47" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="46">
+        <f>SUM(B1-B2)</f>
+        <v>-430</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A6" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="46" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="46" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A8" s="10">
+        <v>46076</v>
+      </c>
+      <c r="B8" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="46">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A9" s="10">
+        <v>46076</v>
+      </c>
+      <c r="B9" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="46">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A10" s="10">
+        <v>46076</v>
+      </c>
+      <c r="B10" s="46" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="46">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A12" s="10">
+        <v>46077</v>
+      </c>
+      <c r="B12" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" s="46">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A13" s="10">
+        <v>46077</v>
+      </c>
+      <c r="B13" s="48" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="46">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A14" s="10">
+        <v>46077</v>
+      </c>
+      <c r="B14" s="48" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="46">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A15" s="10">
+        <v>46077</v>
+      </c>
+      <c r="B15" s="48" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="46">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A16" s="10">
+        <v>46077</v>
+      </c>
+      <c r="B16" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="46">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" s="49" customFormat="1" ht="18.75" customHeight="1">
+      <c r="A18" s="10">
+        <v>46078</v>
+      </c>
+      <c r="B18" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="49">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A19" s="10">
+        <v>46078</v>
+      </c>
+      <c r="B19" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="46">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A20" s="10">
+        <v>46078</v>
+      </c>
+      <c r="B20" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="46">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A21" s="10">
+        <v>46078</v>
+      </c>
+      <c r="B21" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="46">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A22" s="10">
+        <v>46078</v>
+      </c>
+      <c r="B22" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="46">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A23" s="10"/>
+    </row>
+    <row r="24" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A24" s="10">
+        <v>46080</v>
+      </c>
+      <c r="B24" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" s="46">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A26" s="10">
+        <v>46082</v>
+      </c>
+      <c r="B26" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="51">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A28" s="10">
+        <v>46083</v>
+      </c>
+      <c r="B28" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" s="52">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A29" s="10">
+        <v>46083</v>
+      </c>
+      <c r="B29" s="52" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" s="52">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A31" s="10">
+        <v>46084</v>
+      </c>
+      <c r="B31" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31" s="52">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="52" t="s">
+        <v>47</v>
+      </c>
+      <c r="C32" s="52">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="18.75" customHeight="1">
+      <c r="A33" s="10">
+        <v>46084</v>
+      </c>
+      <c r="B33" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33" s="52">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="18.75" customHeight="1">
+      <c r="A35" s="10"/>
+      <c r="B35" s="53"/>
+      <c r="D35" s="53"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D31"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="15.5703125" defaultRowHeight="18.75" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="16.140625" style="53" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" style="53" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="15.5703125" style="53"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="18.75" customHeight="1">
+      <c r="A1" s="54" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="53">
+        <f>2000-430</f>
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="18.75" customHeight="1">
+      <c r="A2" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="53">
+        <f>SUM(C7:C1786)</f>
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="18.75" customHeight="1">
+      <c r="A3" s="54" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="53">
+        <f>SUM(B1-B2)</f>
+        <v>-310</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="18.75" customHeight="1">
+      <c r="A6" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="53" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="18.75" customHeight="1">
+      <c r="A8" s="10">
+        <v>46085</v>
+      </c>
+      <c r="B8" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="53">
+        <v>480</v>
+      </c>
+      <c r="D8" s="53" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="18.75" customHeight="1">
+      <c r="A9" s="10">
+        <v>46085</v>
+      </c>
+      <c r="B9" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="53">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="18.75" customHeight="1">
+      <c r="A10" s="10">
+        <v>46085</v>
+      </c>
+      <c r="B10" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="53">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="18.75" customHeight="1">
+      <c r="A11" s="10">
+        <v>46085</v>
+      </c>
+      <c r="B11" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="53">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="18.75" customHeight="1">
+      <c r="A14" s="10">
+        <v>46086</v>
+      </c>
+      <c r="B14" s="55" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="55">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="18.75" customHeight="1">
+      <c r="A15" s="10">
+        <v>46086</v>
+      </c>
+      <c r="B15" s="55" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="55">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="18.75" customHeight="1">
+      <c r="A16" s="10">
+        <v>46086</v>
+      </c>
+      <c r="B16" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="55">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A18" s="10">
+        <v>46087</v>
+      </c>
+      <c r="B18" s="56" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="56">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A19" s="10">
+        <v>46087</v>
+      </c>
+      <c r="B19" s="56" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="56">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A21" s="10">
+        <v>46088</v>
+      </c>
+      <c r="B21" s="57" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="53">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A23" s="10">
+        <v>46089</v>
+      </c>
+      <c r="B23" s="57" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="57">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A24" s="10">
+        <v>46089</v>
+      </c>
+      <c r="B24" s="57" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="57">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A25" s="10">
+        <v>46089</v>
+      </c>
+      <c r="B25" s="57" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="53">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A27" s="10">
+        <v>46090</v>
+      </c>
+      <c r="B27" s="58" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" s="58">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A28" s="10">
+        <v>46090</v>
+      </c>
+      <c r="B28" s="58" t="s">
+        <v>47</v>
+      </c>
+      <c r="C28" s="58">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A30" s="10">
+        <v>46091</v>
+      </c>
+      <c r="B30" s="58" t="s">
+        <v>26</v>
+      </c>
+      <c r="C30" s="58">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A31" s="10">
+        <v>46091</v>
+      </c>
+      <c r="B31" s="58" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31" s="58">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C31"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="15.5703125" defaultRowHeight="18.75" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="16.140625" style="58" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" style="58" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" style="58" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="15.5703125" style="58"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A1" s="59" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="58">
+        <f>2000-310</f>
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A2" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="58">
+        <f>SUM(C7:C1786)</f>
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A3" s="59" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="58">
+        <f>SUM(B1-B2)</f>
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A6" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="58" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="58" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A8" s="10">
+        <v>46093</v>
+      </c>
+      <c r="B8" s="60" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="58">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A9" s="10">
+        <v>46093</v>
+      </c>
+      <c r="B9" s="60" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="58">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A10" s="10"/>
+    </row>
+    <row r="11" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A11" s="10">
+        <v>46095</v>
+      </c>
+      <c r="B11" s="60" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" s="58">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A13" s="10">
+        <v>46096</v>
+      </c>
+      <c r="B13" s="61" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="58">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A14" s="10">
+        <v>46096</v>
+      </c>
+      <c r="B14" s="61" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="58">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A15" s="10"/>
+    </row>
+    <row r="16" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A16" s="10">
+        <v>46097</v>
+      </c>
+      <c r="B16" s="62" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="62">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A17" s="10">
+        <v>46097</v>
+      </c>
+      <c r="B17" s="62" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="62">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A18" s="10">
+        <v>46097</v>
+      </c>
+      <c r="B18" s="63" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="58">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A19" s="10"/>
+    </row>
+    <row r="20" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A20" s="10">
+        <v>46098</v>
+      </c>
+      <c r="B20" s="63" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="63">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A21" s="10">
+        <v>46098</v>
+      </c>
+      <c r="B21" s="63" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="63">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A23" s="10">
+        <v>46099</v>
+      </c>
+      <c r="B23" s="64" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="64">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A24" s="10">
+        <v>46099</v>
+      </c>
+      <c r="B24" s="64" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="64">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A25" s="10"/>
+    </row>
+    <row r="26" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A26" s="10">
+        <v>46100</v>
+      </c>
+      <c r="B26" s="65" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="65">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A27" s="10">
+        <v>46100</v>
+      </c>
+      <c r="B27" s="65" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="65">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A28" s="10">
+        <v>46100</v>
+      </c>
+      <c r="B28" s="65" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" s="65">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A30" s="10">
+        <v>46101</v>
+      </c>
+      <c r="B30" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" s="66">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A31" s="10">
+        <v>46101</v>
+      </c>
+      <c r="B31" s="66" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31" s="66">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C30"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="15.5703125" defaultRowHeight="18.75" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="16.140625" style="67" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" style="67" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" style="67" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="15.5703125" style="67"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A1" s="68" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="67">
+        <f>2000-10</f>
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A2" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="67">
+        <f>SUM(C7:C1785)</f>
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A3" s="68" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="67">
+        <f>SUM(B1-B2)</f>
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A6" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="67" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A8" s="10">
+        <v>46102</v>
+      </c>
+      <c r="B8" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="67">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A10" s="10">
+        <v>46103</v>
+      </c>
+      <c r="B10" s="67" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="67">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A11" s="10">
+        <v>46103</v>
+      </c>
+      <c r="B11" s="67" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="67">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A12" s="10">
+        <v>46103</v>
+      </c>
+      <c r="B12" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="67">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A13" s="10"/>
+    </row>
+    <row r="14" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A14" s="10">
+        <v>46104</v>
+      </c>
+      <c r="B14" s="70" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="70">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A16" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B16" s="71" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="67">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A17" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B17" s="71" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="67">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A18" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B18" s="71" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" s="67">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A19" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B19" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="67">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A20" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B20" s="71" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="67">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A21" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B21" s="72" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="67">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A22" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B22" s="72" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" s="67">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A24" s="10">
+        <v>46106</v>
+      </c>
+      <c r="B24" s="73" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="67">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A25" s="10">
+        <v>46106</v>
+      </c>
+      <c r="B25" s="73" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="67">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A26" s="10">
+        <v>46106</v>
+      </c>
+      <c r="B26" s="73" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="67">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A27" s="10">
+        <v>46106</v>
+      </c>
+      <c r="B27" s="73" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="67">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A29" s="10"/>
+    </row>
+    <row r="30" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A30" s="10"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C41"/>
@@ -15009,6 +18143,323 @@
     </row>
     <row r="41" spans="1:1" ht="18.75" customHeight="1">
       <c r="A41" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="15.5703125" defaultRowHeight="18.75" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="16.140625" style="74" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" style="74" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" style="74" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="15.5703125" style="74"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A1" s="75" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="74">
+        <f>2000-20</f>
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A2" s="75" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="74">
+        <f>SUM(C7:C1770)</f>
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A3" s="75" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="74">
+        <f>SUM(B1-B2)</f>
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A6" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="74" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A8" s="10">
+        <v>46107</v>
+      </c>
+      <c r="B8" s="74" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="74">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A9" s="10">
+        <v>46107</v>
+      </c>
+      <c r="B9" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="74">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A10" s="10">
+        <v>46107</v>
+      </c>
+      <c r="B10" s="74" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="74">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A11" s="10">
+        <v>46107</v>
+      </c>
+      <c r="B11" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="74">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A12" s="10">
+        <v>46107</v>
+      </c>
+      <c r="B12" s="74" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="74">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A14" s="10">
+        <v>46108</v>
+      </c>
+      <c r="B14" s="76" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="76">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A15" s="10">
+        <v>46108</v>
+      </c>
+      <c r="B15" s="76" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="76">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A16" s="10">
+        <v>46108</v>
+      </c>
+      <c r="B16" s="76" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="76">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="18.75" customHeight="1">
+      <c r="A17" s="10">
+        <v>46108</v>
+      </c>
+      <c r="B17" s="76" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="76">
+        <v>460</v>
+      </c>
+      <c r="D17" s="76" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="18.75" customHeight="1">
+      <c r="A18" s="10">
+        <v>46108</v>
+      </c>
+      <c r="B18" s="76" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="74">
+        <v>750</v>
+      </c>
+      <c r="D18" s="76" t="s">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="15.5703125" defaultRowHeight="18.75" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="16.140625" style="77" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" style="77" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" style="77" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="15.5703125" style="77"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A1" s="78" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="77">
+        <f>2000-30</f>
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A2" s="78" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="77">
+        <f>SUM(C7:C1769)</f>
+        <v>810</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A3" s="78" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="77">
+        <f>SUM(B1-B2)</f>
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A6" s="77" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="77" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A8" s="10"/>
+    </row>
+    <row r="9" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A9" s="10">
+        <v>46109</v>
+      </c>
+      <c r="B9" s="77" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="77">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A10" s="10">
+        <v>46109</v>
+      </c>
+      <c r="B10" s="77" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="77">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A11" s="10">
+        <v>46109</v>
+      </c>
+      <c r="B11" s="77" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="77">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A13" s="10">
+        <v>46110</v>
+      </c>
+      <c r="B13" s="77" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="77">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A14" s="10">
+        <v>46110</v>
+      </c>
+      <c r="B14" s="77" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="77">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A15" s="10">
+        <v>46110</v>
+      </c>
+      <c r="B15" s="79" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="77">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A16" s="10">
+        <v>46110</v>
+      </c>
+      <c r="B16" s="79" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="77">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A17" s="10">
+        <v>46110</v>
+      </c>
+      <c r="B17" s="79" t="s">
+        <v>61</v>
+      </c>
+      <c r="C17" s="77">
+        <v>100</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15751,30 +19202,30 @@
       <c r="A1" s="3"/>
     </row>
     <row r="2" spans="1:9" s="4" customFormat="1" ht="18.75" customHeight="1">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="11">
+      <c r="B2" s="81"/>
+      <c r="C2" s="80">
         <f>SUM(C6:C30)</f>
         <v>300</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="12"/>
-      <c r="I2" s="11">
+      <c r="H2" s="81"/>
+      <c r="I2" s="80">
         <f>SUM(I6:I20)</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="4" customFormat="1" ht="18.75" customHeight="1">
-      <c r="A3" s="12"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="11"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="11"/>
+      <c r="A3" s="81"/>
+      <c r="B3" s="81"/>
+      <c r="C3" s="80"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="80"/>
     </row>
     <row r="5" spans="1:9" ht="18.75" customHeight="1">
       <c r="A5" s="1" t="s">

--- a/depence_bedel.xlsx
+++ b/depence_bedel.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="20730" windowHeight="11760" firstSheet="53" activeTab="60"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="20730" windowHeight="11760" firstSheet="55" activeTab="62"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -68,6 +68,8 @@
     <sheet name="Feuil1 (57)" sheetId="59" r:id="rId59"/>
     <sheet name="Feuil1 (58)" sheetId="60" r:id="rId60"/>
     <sheet name="Feuil1 (59)" sheetId="61" r:id="rId61"/>
+    <sheet name="Feuil1 (60)" sheetId="62" r:id="rId62"/>
+    <sheet name="Feuil1 (61)" sheetId="63" r:id="rId63"/>
   </sheets>
   <calcPr calcId="124519"/>
   <extLst>
@@ -79,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1657" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1710" uniqueCount="76">
   <si>
     <t>depence</t>
   </si>
@@ -302,6 +304,12 @@
   <si>
     <t>Chei5</t>
   </si>
+  <si>
+    <t>USB-C</t>
+  </si>
+  <si>
+    <t>L3SHE</t>
+  </si>
 </sst>
 </file>
 
@@ -351,7 +359,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -577,6 +585,45 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -18323,7 +18370,7 @@
 
 <file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="15.5703125" defaultRowHeight="18.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16.140625" style="77" bestFit="1" customWidth="1"/>
@@ -18346,8 +18393,8 @@
         <v>7</v>
       </c>
       <c r="B2" s="77">
-        <f>SUM(C7:C1769)</f>
-        <v>810</v>
+        <f>SUM(C7:C1770)</f>
+        <v>1880</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="18.75" customHeight="1">
@@ -18356,7 +18403,7 @@
       </c>
       <c r="B3" s="77">
         <f>SUM(B1-B2)</f>
-        <v>1160</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="18.75" customHeight="1">
@@ -18458,6 +18505,567 @@
         <v>61</v>
       </c>
       <c r="C17" s="77">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A19" s="10">
+        <v>46111</v>
+      </c>
+      <c r="B19" s="80" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="80">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" s="81" customFormat="1" ht="18.75" customHeight="1">
+      <c r="A20" s="10">
+        <v>46111</v>
+      </c>
+      <c r="B20" s="81" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="81">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A21" s="10">
+        <v>46111</v>
+      </c>
+      <c r="B21" s="80" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="80">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A22" s="10">
+        <v>46111</v>
+      </c>
+      <c r="B22" s="80" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="80">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A23" s="10">
+        <v>46111</v>
+      </c>
+      <c r="B23" s="80" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="80">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A25" s="10">
+        <v>46112</v>
+      </c>
+      <c r="B25" s="81" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="77">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A26" s="10">
+        <v>46112</v>
+      </c>
+      <c r="B26" s="81" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="77">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A27" s="10">
+        <v>46112</v>
+      </c>
+      <c r="B27" s="81" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="81">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A28" s="10">
+        <v>46112</v>
+      </c>
+      <c r="B28" s="81" t="s">
+        <v>47</v>
+      </c>
+      <c r="C28" s="77">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="15.5703125" defaultRowHeight="18.75" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="16.140625" style="82" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" style="82" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" style="82" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="15.5703125" style="82"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A1" s="83" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="82">
+        <f>2000+90</f>
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A2" s="83" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="82">
+        <f>SUM(C7:C1749)</f>
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A3" s="83" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="82">
+        <f>SUM(B1-B2)</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A6" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="82" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A8" s="10">
+        <v>46113</v>
+      </c>
+      <c r="B8" s="82" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="82">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A9" s="10">
+        <v>46113</v>
+      </c>
+      <c r="B9" s="82" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="82">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A10" s="10">
+        <v>46113</v>
+      </c>
+      <c r="B10" s="82" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="82">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A12" s="10">
+        <v>46114</v>
+      </c>
+      <c r="B12" s="84" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="82">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A13" s="10">
+        <v>46114</v>
+      </c>
+      <c r="B13" s="84" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="82">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A14" s="10">
+        <v>46114</v>
+      </c>
+      <c r="B14" s="84" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="82">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A15" s="10">
+        <v>46114</v>
+      </c>
+      <c r="B15" s="84" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="82">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A16" s="10">
+        <v>46114</v>
+      </c>
+      <c r="B16" s="84" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="82">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" s="85" customFormat="1" ht="18.75" customHeight="1">
+      <c r="A18" s="10">
+        <v>46115</v>
+      </c>
+      <c r="B18" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18" s="85">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A19" s="10">
+        <v>46115</v>
+      </c>
+      <c r="B19" s="85" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="85">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A20" s="10">
+        <v>46115</v>
+      </c>
+      <c r="B20" s="85" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="85">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A21" s="10">
+        <v>46115</v>
+      </c>
+      <c r="B21" s="85" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="85">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A22" s="10">
+        <v>46115</v>
+      </c>
+      <c r="B22" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="85">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A24" s="10">
+        <v>46116</v>
+      </c>
+      <c r="B24" s="86" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="86">
+        <v>90</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C29"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="15.5703125" defaultRowHeight="18.75" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="16.140625" style="87" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" style="87" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" style="87" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="15.5703125" style="87"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A1" s="88" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="87">
+        <f>2000+60</f>
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A2" s="88" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="87">
+        <f>SUM(C7:C1732)</f>
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A3" s="88" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="87">
+        <f>SUM(B1-B2)</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A6" s="87" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="87" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="87" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A8" s="10">
+        <v>46117</v>
+      </c>
+      <c r="B8" s="87" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="87">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A9" s="10">
+        <v>46117</v>
+      </c>
+      <c r="B9" s="87" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" s="87">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A10" s="10">
+        <v>46117</v>
+      </c>
+      <c r="B10" s="87" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="87">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A11" s="10">
+        <v>46117</v>
+      </c>
+      <c r="B11" s="87" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="87">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A12" s="10">
+        <v>46117</v>
+      </c>
+      <c r="B12" s="87" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="87">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A14" s="10">
+        <v>46118</v>
+      </c>
+      <c r="B14" s="89" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="87">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A15" s="10">
+        <v>46118</v>
+      </c>
+      <c r="B15" s="89" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="87">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A16" s="10">
+        <v>46118</v>
+      </c>
+      <c r="B16" s="89" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="87">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A18" s="10">
+        <v>46119</v>
+      </c>
+      <c r="B18" s="90" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="87">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A19" s="10">
+        <v>46119</v>
+      </c>
+      <c r="B19" s="90" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="87">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A20" s="10">
+        <v>46119</v>
+      </c>
+      <c r="B20" s="90" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="87">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A22" s="10">
+        <v>46120</v>
+      </c>
+      <c r="B22" s="91" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="87">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A23" s="10">
+        <v>46120</v>
+      </c>
+      <c r="B23" s="91" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="87">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A24" s="10">
+        <v>46120</v>
+      </c>
+      <c r="B24" s="91" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="87">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A25" s="10">
+        <v>46120</v>
+      </c>
+      <c r="B25" s="91" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" s="87">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A27" s="10">
+        <v>46121</v>
+      </c>
+      <c r="B27" s="92" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="92">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A28" s="10">
+        <v>46121</v>
+      </c>
+      <c r="B28" s="92" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" s="92">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="18.75" customHeight="1">
+      <c r="A29" s="10">
+        <v>46121</v>
+      </c>
+      <c r="B29" s="92" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="92">
         <v>100</v>
       </c>
     </row>
@@ -19202,30 +19810,30 @@
       <c r="A1" s="3"/>
     </row>
     <row r="2" spans="1:9" s="4" customFormat="1" ht="18.75" customHeight="1">
-      <c r="A2" s="81" t="s">
+      <c r="A2" s="94" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="81"/>
-      <c r="C2" s="80">
+      <c r="B2" s="94"/>
+      <c r="C2" s="93">
         <f>SUM(C6:C30)</f>
         <v>300</v>
       </c>
-      <c r="G2" s="81" t="s">
+      <c r="G2" s="94" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="81"/>
-      <c r="I2" s="80">
+      <c r="H2" s="94"/>
+      <c r="I2" s="93">
         <f>SUM(I6:I20)</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="4" customFormat="1" ht="18.75" customHeight="1">
-      <c r="A3" s="81"/>
-      <c r="B3" s="81"/>
-      <c r="C3" s="80"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="80"/>
+      <c r="A3" s="94"/>
+      <c r="B3" s="94"/>
+      <c r="C3" s="93"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="94"/>
+      <c r="I3" s="93"/>
     </row>
     <row r="5" spans="1:9" ht="18.75" customHeight="1">
       <c r="A5" s="1" t="s">
